--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_vol/post_rank_positive_return_rsi_bias_filter/staggered_10d/rsi_10_gt_60__bias_15_gt_-0.02/close/close_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_vol/post_rank_positive_return_rsi_bias_filter/staggered_10d/rsi_10_gt_60__bias_15_gt_-0.02/close/close_annual_metrics.xlsx
@@ -472,12 +472,12 @@
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -560,43 +560,43 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.02296852640717706</v>
+        <v>0.008600425535567391</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>-0.02176047699359285</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.04572397899371805</v>
+        <v>0.03103626649212843</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.25704109303787</v>
+        <v>0.251905391614634</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2258074456632627</v>
+        <v>0.2439986673863632</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.169895372539022</v>
+        <v>0.1047698587492803</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.24401752974416</v>
+        <v>0.1499971678392196</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.2979622884756666</v>
+        <v>0.2049359688658945</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1524278585258237</v>
+        <v>0.2025736951899288</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.1506490308477421</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.140643709668135</v>
+        <v>0.1913836520787712</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.1705329544565692</v>
+        <v>0.04800370553600058</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>18.92796385389877</v>
+        <v>14.63183536937613</v>
       </c>
     </row>
     <row r="3">
@@ -606,43 +606,43 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.1818345327302099</v>
+        <v>-0.1327315443723673</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>-0.2255774308756096</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.05648453427029976</v>
+        <v>0.1198904709197952</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.1917217848444156</v>
+        <v>0.1822549573486103</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.1857954079953912</v>
+        <v>0.1838973631577575</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-1.071999699990973</v>
+        <v>-0.8041461078602944</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-1.494774915655522</v>
+        <v>-1.087627303980251</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.2892861838494236</v>
+        <v>0.6129186621553641</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.2155333507045513</v>
+        <v>0.1843435209008289</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>0.2845881262232945</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.1120422528700713</v>
+        <v>0.09874170215658984</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>-0.8749992724420025</v>
+        <v>-0.7476262974604205</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>16.809469645999</v>
+        <v>12.07412902864274</v>
       </c>
     </row>
     <row r="4">
@@ -652,43 +652,43 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.02326638506584233</v>
+        <v>-0.1563085288059082</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>-0.1141699148043651</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.155149731497159</v>
+        <v>-0.04756963519954949</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.2190250891561956</v>
+        <v>0.155658173444493</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.1928949705836595</v>
+        <v>0.1381003906746615</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.1498606066169341</v>
+        <v>-1.154504425768461</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.234556040586227</v>
+        <v>-1.530886084143385</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0.8543594659084824</v>
+        <v>-0.3456155235804632</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.1795566565611854</v>
+        <v>0.2150270797395929</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0.2177913835362562</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.07507197383771769</v>
+        <v>0.08227565678605708</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.134995646169945</v>
+        <v>-0.7543860292728185</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>18.19773314267326</v>
+        <v>12.4888306811277</v>
       </c>
     </row>
     <row r="5">
@@ -698,43 +698,43 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.05527134950603574</v>
+        <v>-0.03856871458607225</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0.1298071537204202</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-0.1638142426492865</v>
+        <v>-0.1490306268216102</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.2096674040359592</v>
+        <v>0.1950185788456322</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1605431064560986</v>
+        <v>0.1469433385550966</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.2488555091110895</v>
+        <v>-0.1891926335660074</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.3509424215783547</v>
+        <v>-0.2710709505574064</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-1.183680743747748</v>
+        <v>-1.189240528509848</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.2021799012847684</v>
+        <v>0.1794641565138412</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.1515696200238076</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.2823294119299443</v>
+        <v>0.2523090548118714</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>-0.2843426542922929</v>
+        <v>-0.2236104266748029</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>17.48070814010356</v>
+        <v>12.99963025754328</v>
       </c>
     </row>
     <row r="6">
@@ -744,43 +744,43 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.3339557487011648</v>
+        <v>0.07686478399757224</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0.2243203183030871</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.08954799553602899</v>
+        <v>-0.1204386892066688</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.2624377010077943</v>
+        <v>0.156023219721612</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1807227311173247</v>
+        <v>0.1109896292158357</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.21389822974117</v>
+        <v>0.4749483596371369</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.729360463489009</v>
+        <v>0.6369012237086278</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.6056368302456036</v>
+        <v>-1.216486146726677</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.1926139214408998</v>
+        <v>0.09040952386725143</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0.1188658802983931</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.1681620305092143</v>
+        <v>0.1783134294928728</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1.808115396892699</v>
+        <v>0.8828980542410162</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>20.84802321852904</v>
+        <v>13.84286297809181</v>
       </c>
     </row>
     <row r="7">
@@ -790,43 +790,43 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.05631864359128791</v>
+        <v>0.07178426962616369</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>-0.01504143451691176</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.07244982744345263</v>
+        <v>0.08815163113028102</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.3696507226119886</v>
+        <v>0.2804254868356474</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.3079491064305463</v>
+        <v>0.2491661381356121</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.4162409254530341</v>
+        <v>0.5386790712774214</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.555819945710745</v>
+        <v>0.7363774645135339</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.5526482200412469</v>
+        <v>0.6717730937330729</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.2067546288793035</v>
+        <v>0.1660118364278852</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0.127969093077366</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.2087040294006354</v>
+        <v>0.1294002716063131</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.5089481636896555</v>
+        <v>0.8129247356026112</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>21.3508145619308</v>
+        <v>15.55999256915727</v>
       </c>
     </row>
   </sheetData>
